--- a/prospection/prospects-PIWA-500.xlsx
+++ b/prospection/prospects-PIWA-500.xlsx
@@ -7,13 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lot 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prospects" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retirés" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journal envois" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lot 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prospects" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retirés" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prospects'!$A$1:$R$524</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Prospects'!$A$1:$R$524</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -86,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -113,6 +114,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -478,6 +480,371 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="n"/>
+      <c r="B1" s="10" t="n"/>
+      <c r="C1" s="10" t="n"/>
+      <c r="D1" s="10" t="n"/>
+      <c r="E1" s="10" t="n"/>
+      <c r="F1" s="10" t="n"/>
+      <c r="G1" s="10" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Société</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Adresse</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Objet</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Depuis</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Résultat</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Relance prévue le</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Studio218</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>contact@studio218.fr</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ajouter la vidéo à vos offres web, sans recruter</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>YouLoveWords</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>contact@youlovewords.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Transformer vos contenus écrits en vidéos</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Conceptory</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>info@conceptory.fr</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Un renfort motion design pour vos formats sociaux</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Gust</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>contact@agencegust.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Absorber vos pics de production vidéo, en 25 langues</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hula Hoop</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>contact@hula-hoop.fr</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Des vidéos multilingues pour vos clients internationaux</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Adveris</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>contact@adveris.fr</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Des vidéos courtes pour vos campagnes social ads</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Madaré</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>contact@madare.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>La vidéo pour prolonger vos projets de marque</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hi Agency</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>contact@hi-agency.fr</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Un renfort vidéo pour vos marques, en France et en Suisse</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -579,7 +946,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>En attente : adresse mail introuvable</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr"/>
@@ -625,10 +992,14 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
+          <t>Envoyé</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="260" customHeight="1">
@@ -671,11 +1042,15 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>Non envoyé</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Écarté : semble être un lieu de séminaires, pas une agence</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="260" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -717,10 +1092,14 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
+          <t>Envoyé</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
       <c r="I5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="260" customHeight="1">
@@ -763,7 +1142,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>En attente : adresse mail introuvable</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
@@ -809,7 +1188,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>En attente : adresse mail introuvable</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
@@ -855,7 +1234,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>En attente : adresse mail introuvable</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
@@ -901,7 +1280,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>En attente : adresse mail introuvable</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
@@ -947,7 +1326,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>En attente : adresse mail introuvable</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
@@ -993,7 +1372,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>En attente : adresse mail introuvable</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
@@ -1039,7 +1418,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>En attente : adresse mail introuvable</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
@@ -1085,7 +1464,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>En attente : adresse mail introuvable</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
@@ -1131,7 +1510,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>En attente : adresse mail introuvable</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
@@ -1177,7 +1556,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>En attente : adresse mail introuvable</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
@@ -1223,7 +1602,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>En attente : adresse mail introuvable</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr"/>
@@ -1269,7 +1648,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>En attente : adresse mail introuvable</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
@@ -1315,7 +1694,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>En attente : adresse mail introuvable</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
@@ -1361,7 +1740,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>En attente : adresse mail introuvable</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
@@ -1407,7 +1786,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Prêt, non envoyé</t>
+          <t>En attente : adresse mail introuvable</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr"/>
@@ -1418,7 +1797,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1708,10 +2087,14 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr"/>
+          <t>Envoyé</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
       <c r="R3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="110" customHeight="1">
@@ -1796,10 +2179,14 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr"/>
+          <t>Envoyé</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
       <c r="R4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="110" customHeight="1">
@@ -1884,10 +2271,14 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr"/>
+          <t>Envoyé</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
       <c r="R5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="110" customHeight="1">
@@ -2060,10 +2451,14 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr"/>
+          <t>Envoyé</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
       <c r="R7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="110" customHeight="1">
@@ -2148,10 +2543,14 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr"/>
+          <t>Envoyé</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
       <c r="R8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="110" customHeight="1">
@@ -2324,10 +2723,14 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr"/>
+          <t>Envoyé</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
       <c r="R10" s="3" t="inlineStr"/>
     </row>
     <row r="11" ht="110" customHeight="1">
@@ -2412,10 +2815,14 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr"/>
+          <t>Envoyé</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
       <c r="R11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="110" customHeight="1">
@@ -2676,10 +3083,14 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr"/>
+          <t>Envoyé</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
       <c r="R14" s="3" t="inlineStr"/>
     </row>
     <row r="15" ht="110" customHeight="1">
@@ -49050,7 +49461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -49187,7 +49598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/prospection/prospects-PIWA-500.xlsx
+++ b/prospection/prospects-PIWA-500.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -829,6 +829,80 @@
         </is>
       </c>
       <c r="G10" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Gravotech</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>contact@gravotech.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Préparer Global Industrie 2027 en vidéo</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Envoyé (adresse publiée dans leurs mentions légales)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vates</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sales@vates.tech</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Une vidéo pour présenter Vates après votre levée de 30 M€</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Envoyé (adresse publiée sur leur site d'aide)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>12/10/2026</t>
         </is>
@@ -3703,10 +3777,14 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr"/>
+          <t>Envoyé</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
       <c r="R21" s="3" t="inlineStr"/>
     </row>
     <row r="22" ht="110" customHeight="1">
@@ -5314,10 +5392,14 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr"/>
+          <t>Envoyé</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
       <c r="R39" s="3" t="inlineStr"/>
     </row>
     <row r="40" ht="110" customHeight="1">

--- a/prospection/prospects-PIWA-500.xlsx
+++ b/prospection/prospects-PIWA-500.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -903,6 +903,956 @@
         </is>
       </c>
       <c r="G12" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pickers</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>contact@agence-pickers.fr</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Espaces Atypiques</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>contact@espaces-atypiques.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Vulcania</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>bienvenue@vulcania.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fermob</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>info@fermob.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Festival des Vieilles Charrues</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>info@vieillescharrues.asso.fr</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Office de Tourisme du Lac d'Annecy</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>info@lac-annecy.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Aura Aero</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>contact@aura-aero.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Quobly</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>contact@quobly.io</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GitGuardian</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>contact@gitguardian.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kipli</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>hello@kipli.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Groupe Giboire</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>communication@giboire.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Gobelins Paris</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>info-il@gobelins.fr</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ÉCHEC : bloqué par le serveur du destinataire</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Voltalia</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>contact@voltalia.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ÉCHEC : bloqué par le serveur du destinataire</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Maisons du Monde</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>presse@maisonsdumonde.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Puy du Fou</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>servicepresse@puydufou.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Groupe Barrière</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>contact-presse@groupebarriere.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Groupe Rocher</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>press@yr.net</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ÉCHEC : adresse inexistante</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rubis</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>presse@rubis.fr</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Latécoère</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>latecoeregroupcommunication@latecoere.aero</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Asmodee</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>press@asmodee.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mecachrome</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>communication@mecachromegroup.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Lectra</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>presse@lectra.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Trigano</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>communication@trigano.fr</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Figeac Aéro</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>communications.group@figeac-aero.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Lacroix Group</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>info@lacroix-group.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Groupe Guillin</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>contact@groupeguillin.fr</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>(personnalisé)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>12/10/2026</t>
         </is>

--- a/prospection/prospects-PIWA-500.xlsx
+++ b/prospection/prospects-PIWA-500.xlsx
@@ -1346,7 +1346,6 @@
           <t>ÉCHEC : bloqué par le serveur du destinataire</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1379,7 +1378,6 @@
           <t>ÉCHEC : bloqué par le serveur du destinataire</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1523,7 +1521,6 @@
           <t>ÉCHEC : adresse inexistante</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1959,6 +1956,13 @@
           <t>Bonjour,
 Vous exposez au SIAL Paris du 17 au 21 octobre (Hall 5A). Une vidéo courte qui tourne en boucle sur le stand attire l'œil des acheteurs et présente vos marques en quelques secondes, en français et en anglais.
 Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nos équipes peuvent encore livrer avant l'ouverture du salon si nous démarrons cette semaine : script, animation, musique, à partir de 690 € HT.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2005,6 +2009,13 @@
           <t>Bonjour,
 Vos clients PME vous confient leur site et leur référencement. Une vidéo de présentation en page d'accueil augmente le temps passé sur le site et les demandes de contact.
 Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous produisons en marque blanche, dans la charte de vos clients, et vous fixez votre prix de revente.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2055,6 +2066,13 @@
           <t>Bonjour,
 Vous accompagnez vos clients en communication et en développement commercial depuis plus de 20 ans. La vidéo est souvent le format qui manque pour leurs présentations et leurs recrutements.
 Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous produisons en marque blanche, livré en 7 jours, et vous gardez la relation client.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2105,6 +2123,13 @@
           <t>Bonjour,
 Votre réseau de rédacteurs produit des contenus de qualité pour vos clients. Les mêmes messages, transformés en vidéos courtes, sont repris bien plus sur LinkedIn et Instagram.
 Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous pouvons produire ces vidéos en marque blanche à partir de vos textes, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2155,6 +2180,13 @@
           <t>Bonjour,
 Vos campagnes inbound et social media convertissent mieux avec de la vidéo, mais la production prend du temps à une équipe marketing.
 Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous livrons des vidéos courtes en 7 jours, en marque blanche, prêtes pour vos campagnes clients.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2201,6 +2233,13 @@
           <t>Bonjour,
 Vous gérez le social media, le SEA et des campagnes TV et DOOH pour vos clients. Les pics de production vidéo sont difficiles à absorber sans studio interne.
 Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous produisons vos vidéos motion design en marque blanche, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2247,6 +2286,13 @@
           <t>Bonjour,
 Vous faites du storytelling et du contenu pour vos clients. La vidéo motion design prolonge naturellement ce travail sur les réseaux sociaux.
 Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous produisons en marque blanche à partir de vos scripts ou des nôtres, livré en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2292,7 +2338,14 @@
         <is>
           <t>Bonjour,
 Félicitations pour votre série A de 10 M€. Expliquer des employés IA autonomes en 45 secondes, en France comme aux États-Unis, est exactement le rôle d'une vidéo motion design.
-Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous livrons en 7 jours, en français et en anglais, à partir de 990 € HT.
+Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous livrons en 7 jours, en français et en anglais, à partir de 390 € HT.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2338,7 +2391,14 @@
         <is>
           <t>Bonjour,
 Félicitations pour votre levée de 2,2 M€. Pour renforcer l'équipe commerciale, une vidéo de démonstration de la gestion de flotte facilite chaque premier rendez-vous.
-Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous livrons en 7 jours, à partir de 990 € HT.
+Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous livrons en 7 jours, à partir de 390 € HT.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2384,7 +2444,14 @@
         <is>
           <t>Bonjour,
 Félicitations pour votre levée d'amorçage. Une vidéo claire sur le choix entre réparation, réemploi et recyclage aide votre future force commerciale à convaincre les industriels.
-Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous livrons en 7 jours, à partir de 990 € HT.
+Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous livrons en 7 jours, à partir de 390 € HT.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2430,7 +2497,14 @@
         <is>
           <t>Bonjour,
 Félicitations pour votre série A avec Partech. Le lancement du mode 3D est une belle occasion de montrer Rayon en action aux designers et architectes, en plusieurs langues.
-Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous livrons en 7 jours, à partir de 990 € HT.
+Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous livrons en 7 jours, à partir de 390 € HT.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2477,6 +2551,13 @@
           <t>Bonjour,
 Félicitations pour votre série A. Avec 70 % de clients hors de France, une vidéo explicative déclinée en plusieurs langues aide vos équipes à présenter Marble aux banques et fintechs.
 Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous livrons en 7 jours, chaque langue supplémentaire à 90 € HT.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2523,6 +2604,13 @@
           <t>Bonjour,
 Félicitations pour votre série B. Pour vous lancer en Europe, en Asie et au Moyen-Orient, une vidéo explicative de votre plateforme, déclinée dans chaque langue, accompagne vos équipes commerciales.
 Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous livrons en 7 jours, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2569,6 +2657,13 @@
           <t>Bonjour,
 Félicitations pour votre levée de 11 M€. Pour l'Amérique du Nord et l'Asie, une vidéo motion design qui montre simplement comment vos robots voient et s'adaptent parle à tous les industriels.
 Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous livrons en 7 jours, en plusieurs langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2615,6 +2710,13 @@
           <t>Bonjour,
 Félicitations pour la mise en vente de Mallow. Les parents découvrent ce type de produit sur Instagram et TikTok : des pubs vidéo courtes et rythmées sont le meilleur moyen de le faire comprendre.
 Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous livrons en 7 jours, à partir de 390 € HT la vidéo courte.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2661,6 +2763,13 @@
           <t>Bonjour,
 Votre réseau grandit vite dans l'Ouest. Chaque ouverture de club a besoin de vidéos de pré-ouverture et de promotion locale, et le recrutement de franchisés aussi.
 Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous proposons un abonnement de 4 vidéos par mois à 890 € HT, déclinables club par club.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2707,6 +2816,13 @@
           <t>Bonjour,
 Vous visez 30 nouvelles agences en 2026. Une vidéo qui explique le métier de courtier en travaux en une minute rassure les candidats et les clients.
 Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous livrons en 7 jours, et proposons un abonnement à 890 € HT par mois pour le réseau.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2753,6 +2869,13 @@
           <t>Bonjour,
 Vous accélérez la franchise et visez 120 agences d'ici 2030. Les biens atypiques se racontent en vidéo, et le recrutement de franchisés aussi.
 Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous livrons en 7 jours, avec un abonnement possible à 890 € HT par mois pour le réseau.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2799,6 +2922,13 @@
           <t>Bonjour,
 Vous êtes inscrits à Global Industrie Lyon 2027 et réalisez l'essentiel de votre activité à l'international. Une vidéo de stand et de présentation produit, déclinée dans les langues de vos filiales, sert toute l'année.
 Nos équipes réalisent des vidéos motion design : script, voix off, musique et animation, livrées en 7 jours, dans plus de 25 langues. Nous livrons en 7 jours, chaque langue supplémentaire à 90 € HT.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Seriez vous disponible pour un échange de 10 minutes cette semaine ?
 Bien cordialement,
@@ -2998,8 +3128,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Haudecoeur. Nos équipes réalisent des vidéos motion design pour les entreprises : marque employeur, recrutement, présentation de produits et vidéos de stand pour les salons, livrées en 7 jours, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo réalisée pour un acteur du bâtiment : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
+Vidéo de présentation à partir de 390 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -3086,6 +3223,13 @@
           <t>Bonjour,
 Je me permets de contacter Conceptory. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -3178,6 +3322,13 @@
           <t>Bonjour,
 Je me permets de contacter Gust. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -3270,6 +3421,13 @@
           <t>Bonjour,
 Je me permets de contacter Hula Hoop. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -3362,6 +3520,13 @@
           <t>Bonjour,
 Je me permets de contacter NOIISE. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -3450,6 +3615,13 @@
           <t>Bonjour,
 Je me permets de contacter Adveris. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -3542,6 +3714,13 @@
           <t>Bonjour,
 Je me permets de contacter Madaré. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -3634,6 +3813,13 @@
           <t>Bonjour,
 Je me permets de contacter MO&amp;JO. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -3722,6 +3908,13 @@
           <t>Bonjour,
 Je me permets de contacter Hi Agency. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -3814,6 +4007,13 @@
           <t>Bonjour,
 Je me permets de contacter Studio218. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -3906,6 +4106,13 @@
           <t>Bonjour,
 Je me permets de contacter L'Arbre de Mai. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -3994,6 +4201,13 @@
           <t>Bonjour,
 Je me permets de contacter Stride-up. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -4082,6 +4296,13 @@
           <t>Bonjour,
 Je me permets de contacter YouLoveWords. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -4174,6 +4395,13 @@
           <t>Bonjour,
 Je me permets de contacter Tactee. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -4262,6 +4490,13 @@
           <t>Bonjour,
 Je me permets de contacter Olympe Digital. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -4350,8 +4585,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Delos si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Delos si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -4438,8 +4680,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Opio si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Opio si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -4526,8 +4775,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour SoonGo si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour SoonGo si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -4614,8 +4870,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Cleavr si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Cleavr si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -4702,8 +4965,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Vates si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Vates si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -4794,8 +5064,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Mallow si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Mallow si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -4882,8 +5159,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Rayon si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Rayon si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -4970,8 +5254,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Marble si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Marble si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -5058,8 +5349,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Revalue si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Revalue si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -5146,8 +5444,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Hackuity si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Hackuity si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -5234,8 +5539,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Pivot si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Pivot si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -5322,8 +5634,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Inbolt si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Inbolt si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -5410,8 +5729,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Axomove si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Axomove si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -5498,8 +5824,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour DiappyMed si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour DiappyMed si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -5586,8 +5919,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Laboratoires üma si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Laboratoires üma si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -5678,6 +6018,13 @@
           <t>Bonjour,
 Je contacte Espaces Atypiques au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -5770,6 +6117,13 @@
           <t>Bonjour,
 Je contacte Wefit.club au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -5862,6 +6216,13 @@
           <t>Bonjour,
 Je contacte Gigafit au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -5954,6 +6315,13 @@
           <t>Bonjour,
 Je contacte Domicile Clean au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -6046,6 +6414,13 @@
           <t>Bonjour,
 Je contacte illiCO travaux au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -6138,6 +6513,13 @@
           <t>Bonjour,
 Je contacte Anacours au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -6230,6 +6612,13 @@
           <t>Bonjour,
 Je contacte King Marcel au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -6317,8 +6706,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Gravotech. Nos équipes réalisent des vidéos motion design pour les entreprises : marque employeur, recrutement, présentation de produits et vidéos de stand pour les salons, livrées en 7 jours, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo réalisée pour un acteur du bâtiment : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
+Vidéo de présentation à partir de 390 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -6413,6 +6809,13 @@
           <t>Bonjour,
 Je me permets de contacter Target Web. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -6505,6 +6908,13 @@
           <t>Bonjour,
 Je me permets de contacter citron plume. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -6597,6 +7007,13 @@
           <t>Bonjour,
 Je me permets de contacter Com'Only. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -6689,6 +7106,13 @@
           <t>Bonjour,
 Je me permets de contacter FHCOM Influence &amp; Réputation. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -6781,6 +7205,13 @@
           <t>Bonjour,
 Je me permets de contacter Agence Léon. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -6873,6 +7304,13 @@
           <t>Bonjour,
 Je me permets de contacter ETH Digital. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -6965,6 +7403,13 @@
           <t>Bonjour,
 Je me permets de contacter Yucatan. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -7057,6 +7502,13 @@
           <t>Bonjour,
 Je me permets de contacter Social Media Pro. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -7149,6 +7601,13 @@
           <t>Bonjour,
 Je me permets de contacter Chalvin Paris. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -7241,6 +7700,13 @@
           <t>Bonjour,
 Je me permets de contacter ODW. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -7333,6 +7799,13 @@
           <t>Bonjour,
 Je me permets de contacter WOO. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -7425,6 +7898,13 @@
           <t>Bonjour,
 Je me permets de contacter Idaos. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -7517,6 +7997,13 @@
           <t>Bonjour,
 Je me permets de contacter Zebrure. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -7609,6 +8096,13 @@
           <t>Bonjour,
 Je me permets de contacter Public Actif. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -7701,6 +8195,13 @@
           <t>Bonjour,
 Je me permets de contacter Taste. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -7793,6 +8294,13 @@
           <t>Bonjour,
 Je me permets de contacter 360 Webmarketing. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -7885,6 +8393,13 @@
           <t>Bonjour,
 Je me permets de contacter Linker. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -7977,6 +8492,13 @@
           <t>Bonjour,
 Je me permets de contacter Million Marketing. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -8069,6 +8591,13 @@
           <t>Bonjour,
 Je me permets de contacter Archipel Marketing. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -8161,6 +8690,13 @@
           <t>Bonjour,
 Je me permets de contacter Bew Web Agency. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -8253,6 +8789,13 @@
           <t>Bonjour,
 Je me permets de contacter Wedezign. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -8345,6 +8888,13 @@
           <t>Bonjour,
 Je me permets de contacter SIITEO. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -8437,6 +8987,13 @@
           <t>Bonjour,
 Je me permets de contacter BH Internet. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -8529,6 +9086,13 @@
           <t>Bonjour,
 Je me permets de contacter 4Beez. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -8621,6 +9185,13 @@
           <t>Bonjour,
 Je me permets de contacter Simplébo. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -8713,6 +9284,13 @@
           <t>Bonjour,
 Je me permets de contacter Fidesio. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -8805,6 +9383,13 @@
           <t>Bonjour,
 Je me permets de contacter ACRV. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -8897,6 +9482,13 @@
           <t>Bonjour,
 Je me permets de contacter La Crème French. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -8989,6 +9581,13 @@
           <t>Bonjour,
 Je me permets de contacter Fanfare. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -9081,6 +9680,13 @@
           <t>Bonjour,
 Je me permets de contacter La Suite and Co. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -9173,6 +9779,13 @@
           <t>Bonjour,
 Je me permets de contacter Les Têtes de Pub. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -9265,6 +9878,13 @@
           <t>Bonjour,
 Je me permets de contacter Agence Comquest. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -9357,6 +9977,13 @@
           <t>Bonjour,
 Je me permets de contacter Metalyde. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -9449,6 +10076,13 @@
           <t>Bonjour,
 Je me permets de contacter La Chose. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -9541,6 +10175,13 @@
           <t>Bonjour,
 Je me permets de contacter Ici Barbès. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -9633,6 +10274,13 @@
           <t>Bonjour,
 Je me permets de contacter Bronx. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -9725,6 +10373,13 @@
           <t>Bonjour,
 Je me permets de contacter Procom'Paris. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -9817,6 +10472,13 @@
           <t>Bonjour,
 Je me permets de contacter bb&amp;b. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -9909,6 +10571,13 @@
           <t>Bonjour,
 Je me permets de contacter Growth Room. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -10001,6 +10670,13 @@
           <t>Bonjour,
 Je me permets de contacter Pickers. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -10093,6 +10769,13 @@
           <t>Bonjour,
 Je me permets de contacter Agence Babel. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -10185,6 +10868,13 @@
           <t>Bonjour,
 Je me permets de contacter Les Causantes. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -10277,6 +10967,13 @@
           <t>Bonjour,
 Je me permets de contacter sercopointweb. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -10369,6 +11066,13 @@
           <t>Bonjour,
 Je me permets de contacter plus2sens. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -10461,6 +11165,13 @@
           <t>Bonjour,
 Je me permets de contacter Dufresne Corrigan Scarlett. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -10553,6 +11264,13 @@
           <t>Bonjour,
 Je me permets de contacter Hey Oh. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -10645,6 +11363,13 @@
           <t>Bonjour,
 Je me permets de contacter THRIVE. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -10737,6 +11462,13 @@
           <t>Bonjour,
 Je me permets de contacter Agence Bloom. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -10829,6 +11561,13 @@
           <t>Bonjour,
 Je me permets de contacter Symbioz. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -10921,6 +11660,13 @@
           <t>Bonjour,
 Je me permets de contacter Adrénaline. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -11013,6 +11759,13 @@
           <t>Bonjour,
 Je me permets de contacter Wapiti. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -11105,6 +11858,13 @@
           <t>Bonjour,
 Je me permets de contacter CO2 Communication. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -11197,6 +11957,13 @@
           <t>Bonjour,
 Je me permets de contacter Audience Agency. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -11289,6 +12056,13 @@
           <t>Bonjour,
 Je me permets de contacter Agence Pistache. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -11381,6 +12155,13 @@
           <t>Bonjour,
 Je me permets de contacter Sublimeo. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -11473,6 +12254,13 @@
           <t>Bonjour,
 Je me permets de contacter CodeKitchen. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -11565,6 +12353,13 @@
           <t>Bonjour,
 Je me permets de contacter IMAGIC. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -11657,6 +12452,13 @@
           <t>Bonjour,
 Je me permets de contacter Phileas. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -11749,6 +12551,13 @@
           <t>Bonjour,
 Je me permets de contacter Esilab. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -11841,6 +12650,13 @@
           <t>Bonjour,
 Je me permets de contacter Dagré Communication. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -11933,6 +12749,13 @@
           <t>Bonjour,
 Je me permets de contacter Wooz'up. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -12025,6 +12848,13 @@
           <t>Bonjour,
 Je me permets de contacter Joli Rouge. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -12117,6 +12947,13 @@
           <t>Bonjour,
 Je me permets de contacter WONDERFUL. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -12209,6 +13046,13 @@
           <t>Bonjour,
 Je me permets de contacter Paloha. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -12301,6 +13145,13 @@
           <t>Bonjour,
 Je me permets de contacter Teaser. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -12393,6 +13244,13 @@
           <t>Bonjour,
 Je me permets de contacter Babouche. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -12485,6 +13343,13 @@
           <t>Bonjour,
 Je me permets de contacter OCAMPO France. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -12577,6 +13442,13 @@
           <t>Bonjour,
 Je me permets de contacter Gazelle Communication. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -12669,6 +13541,13 @@
           <t>Bonjour,
 Je me permets de contacter Derrière les Pixels. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -12761,6 +13640,13 @@
           <t>Bonjour,
 Je me permets de contacter Matt Design &amp; Communication. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -12853,6 +13739,13 @@
           <t>Bonjour,
 Je me permets de contacter My Creative Agency (MCA). Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -12945,6 +13838,13 @@
           <t>Bonjour,
 Je me permets de contacter LATELIER. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -13037,6 +13937,13 @@
           <t>Bonjour,
 Je me permets de contacter addictic. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -13129,6 +14036,13 @@
           <t>Bonjour,
 Je me permets de contacter Cloüet Communication. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -13221,6 +14135,13 @@
           <t>Bonjour,
 Je me permets de contacter Imaginactif. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -13313,6 +14234,13 @@
           <t>Bonjour,
 Je me permets de contacter Oui L'agence. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -13405,6 +14333,13 @@
           <t>Bonjour,
 Je me permets de contacter Partenaires d'Avenir. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -13497,6 +14432,13 @@
           <t>Bonjour,
 Je me permets de contacter Propulse. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -13589,6 +14531,13 @@
           <t>Bonjour,
 Je me permets de contacter Overscan. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -13681,6 +14630,13 @@
           <t>Bonjour,
 Je me permets de contacter Graphonik. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -13773,6 +14729,13 @@
           <t>Bonjour,
 Je me permets de contacter Ignis. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -13865,6 +14828,13 @@
           <t>Bonjour,
 Je me permets de contacter Rivacom. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -13957,6 +14927,13 @@
           <t>Bonjour,
 Je me permets de contacter D'une idée l'autre. Nos équipes réalisent des vidéos motion design pour les entreprises : présentation, produit, publicité, recrutement, avec voix off et musique, dans plus de 25 langues, livrées en 7 jours.
 Nous travaillons aussi en marque blanche pour les agences : vous gardez la relation client, nous produisons dans votre charte, sans mention de notre nom. Utile pour absorber un pic de charge ou proposer de la vidéo sans recruter.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Quelques réalisations ici : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Tarifs partenaires dégressifs selon le volume. Seriez vous ouverts à un premier projet test ?
 Bien cordialement,
@@ -14049,8 +15026,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Lupin Dental si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Lupin Dental si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -14141,8 +15125,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Korben Robots si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Korben Robots si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -14233,8 +15224,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Huscarl si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Huscarl si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -14325,8 +15323,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Viraj Aero si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Viraj Aero si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -14417,8 +15422,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Blacknut si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Blacknut si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -14509,8 +15521,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Tissium si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Tissium si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -14601,8 +15620,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Caviar de Neuvic si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Caviar de Neuvic si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -14693,8 +15719,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour ColibriTD si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour ColibriTD si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -14785,8 +15818,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Swiftask si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Swiftask si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -14877,8 +15917,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Murena si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Murena si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -14969,8 +16016,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Therasonic si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Therasonic si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -15061,8 +16115,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Oteo Care si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Oteo Care si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -15153,8 +16214,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Abyssa si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Abyssa si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -15245,8 +16313,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour ArcSpace si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour ArcSpace si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -15337,8 +16412,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Arlequin AI si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Arlequin AI si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -15429,8 +16511,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Actionable si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Actionable si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -15521,8 +16610,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Horizom si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Horizom si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -15613,8 +16709,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour AAIS (Armageddon Artificial Intelligence Security) si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour AAIS (Armageddon Artificial Intelligence Security) si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -15705,8 +16808,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour BlueSecure si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour BlueSecure si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -15797,8 +16907,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour HighLife si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour HighLife si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -15889,8 +17006,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Biolevate si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Biolevate si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -15981,8 +17105,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Wealthcome si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Wealthcome si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -16073,8 +17204,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Incepto Medical si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Incepto Medical si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -16165,8 +17303,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Kheops si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Kheops si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -16257,8 +17402,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Zeliq si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Zeliq si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -16349,8 +17501,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Primo si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Primo si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -16441,8 +17600,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Lightspring si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Lightspring si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -16533,8 +17699,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Reecall si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Reecall si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -16625,8 +17798,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Akira si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Akira si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -16717,8 +17897,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Amoéba si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Amoéba si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -16809,8 +17996,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Graneet si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Graneet si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -16901,8 +18095,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Wiremind si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Wiremind si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -16993,8 +18194,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour vorteX-io si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour vorteX-io si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -17085,8 +18293,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Quobly si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Quobly si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -17177,8 +18392,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour AlpSemi si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour AlpSemi si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -17269,8 +18491,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Univity si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Univity si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -17361,8 +18590,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Aura Aero si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Aura Aero si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -17453,8 +18689,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour UroMems si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour UroMems si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -17545,8 +18788,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Alan si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Alan si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -17637,8 +18887,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Pasqal si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Pasqal si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -17729,8 +18986,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour AMI Labs si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour AMI Labs si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -17821,8 +19085,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Pennylane si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Pennylane si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -17913,8 +19184,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Harmattan AI si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Harmattan AI si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -18005,8 +19283,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour DentalMonitoring si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour DentalMonitoring si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -18097,8 +19382,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Naboo si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Naboo si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -18189,8 +19481,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Hummingbirds si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Hummingbirds si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -18281,8 +19580,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour GitGuardian si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour GitGuardian si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -18373,8 +19679,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour LegalPlace si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour LegalPlace si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -18465,8 +19778,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Dust si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Dust si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -18557,8 +19877,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Kervalion si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Kervalion si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -18649,8 +19976,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour VizioSense si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour VizioSense si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -18741,8 +20075,15 @@
           <t>Bonjour,
 Félicitations pour votre récente levée de fonds. Une phase de croissance demande souvent des vidéos claires pour expliquer le produit, accompagner les recrutements et les démos commerciales.
 Nos équipes réalisent des vidéos motion design (script, voix off, musique, animation) livrées en 7 jours, dans plus de 25 langues pour l'international.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite pour Loumo si cela vous intéresse.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite pour Loumo si cela vous intéresse.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -18832,6 +20173,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Respire. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -18923,6 +20271,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Horace. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -19014,6 +20369,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Kipli. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -19105,6 +20467,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Japhy. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -19196,6 +20565,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Joone. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -19287,6 +20663,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Gemmyo. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -19378,6 +20761,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Le Slip Français. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -19469,6 +20859,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Asphalte. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -19560,6 +20957,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Cabaïa. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -19651,6 +21055,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Tediber. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -19742,6 +21153,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Nutri&amp;Co. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -19833,6 +21251,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Miliboo. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -19924,6 +21349,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Hopaal. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -20015,6 +21447,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Neo by Nature. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -20106,6 +21545,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Blissim. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -20197,6 +21643,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Jo Bigorneau. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -20288,6 +21741,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Sézane. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -20379,6 +21839,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Jimmy Fairly. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -20470,6 +21937,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Typology. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -20561,6 +22035,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Merci Handy. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -20652,6 +22133,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Le Petit Ballon. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -20743,6 +22231,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Michel et Augustin. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -20834,6 +22329,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Loom. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -20925,6 +22427,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter 1083. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -21016,6 +22525,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Faguo. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -21107,6 +22623,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Polette. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -21198,6 +22721,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Aime. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -21289,6 +22819,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Feed.. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -21380,6 +22917,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Nutripure. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -21471,6 +23015,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter BonneGueule. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -21562,6 +23113,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Balzac Paris. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -21653,6 +23211,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Rouje. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -21744,6 +23309,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter La Belle Boucle. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -21835,6 +23407,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Le Bon Graillon. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -21926,6 +23505,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Pimpant. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -22017,6 +23603,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Lamazuna. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -22108,6 +23701,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Cuure. Nos équipes réalisent des vidéos publicitaires courtes en motion design pour les marques : pubs Meta et TikTok, vidéos produit, déclinaisons en plus de 25 langues pour l'export, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo courte à partir de 390 € HT, ou abonnement à 890 € HT par mois pour 4 vidéos. Seriez vous ouverts à un premier test ?
 Bien cordialement,
@@ -22200,6 +23800,13 @@
           <t>Bonjour,
 Je contacte Nestenn au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -22292,6 +23899,13 @@
           <t>Bonjour,
 Je contacte Human Immobilier au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -22384,6 +23998,13 @@
           <t>Bonjour,
 Je contacte Fitness Park au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -22476,6 +24097,13 @@
           <t>Bonjour,
 Je contacte Acadomia au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -22568,6 +24196,13 @@
           <t>Bonjour,
 Je contacte ECF (École de Conduite Française) au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -22660,6 +24295,13 @@
           <t>Bonjour,
 Je contacte Bodyminute au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -22752,6 +24394,13 @@
           <t>Bonjour,
 Je contacte Franck Provost au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -22844,6 +24493,13 @@
           <t>Bonjour,
 Je contacte Optical Center au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -22931,8 +24587,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter STEF. Nos équipes réalisent des vidéos motion design pour les entreprises : marque employeur, recrutement, présentation de produits et vidéos de stand pour les salons, livrées en 7 jours, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo réalisée pour un acteur du bâtiment : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
+Vidéo de présentation à partir de 390 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -23018,8 +24681,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter ID Logistics. Nos équipes réalisent des vidéos motion design pour les entreprises : marque employeur, recrutement, présentation de produits et vidéos de stand pour les salons, livrées en 7 jours, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo réalisée pour un acteur du bâtiment : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
+Vidéo de présentation à partir de 390 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -23105,8 +24775,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Verkor. Nos équipes réalisent des vidéos motion design pour les entreprises : marque employeur, recrutement, présentation de produits et vidéos de stand pour les salons, livrées en 7 jours, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo réalisée pour un acteur du bâtiment : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
+Vidéo de présentation à partir de 390 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -23192,8 +24869,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Altho (Brets). Nos équipes réalisent des vidéos motion design pour les entreprises : marque employeur, recrutement, présentation de produits et vidéos de stand pour les salons, livrées en 7 jours, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo réalisée pour un acteur du bâtiment : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
+Vidéo de présentation à partir de 390 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -23279,8 +24963,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Prodways Group (filiale Initial). Nos équipes réalisent des vidéos motion design pour les entreprises : marque employeur, recrutement, présentation de produits et vidéos de stand pour les salons, livrées en 7 jours, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo réalisée pour un acteur du bâtiment : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
+Vidéo de présentation à partir de 390 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -23366,8 +25057,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Rairies Montrieux. Nos équipes réalisent des vidéos motion design pour les entreprises : marque employeur, recrutement, présentation de produits et vidéos de stand pour les salons, livrées en 7 jours, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo réalisée pour un acteur du bâtiment : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
+Vidéo de présentation à partir de 390 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -23453,8 +25151,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Millet Portes et Fenêtres (Groupe Millet). Nos équipes réalisent des vidéos motion design pour les entreprises : marque employeur, recrutement, présentation de produits et vidéos de stand pour les salons, livrées en 7 jours, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo réalisée pour un acteur du bâtiment : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
+Vidéo de présentation à partir de 390 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -23540,8 +25245,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter MILLS. Nos équipes réalisent des vidéos motion design pour les entreprises : marque employeur, recrutement, présentation de produits et vidéos de stand pour les salons, livrées en 7 jours, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo réalisée pour un acteur du bâtiment : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
+Vidéo de présentation à partir de 390 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -23627,8 +25339,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Bel'M. Nos équipes réalisent des vidéos motion design pour les entreprises : marque employeur, recrutement, présentation de produits et vidéos de stand pour les salons, livrées en 7 jours, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo réalisée pour un acteur du bâtiment : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
+Vidéo de présentation à partir de 390 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -23719,6 +25438,13 @@
           <t>Bonjour,
 Je contacte Black &amp; White Burger au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -23811,6 +25537,13 @@
           <t>Bonjour,
 Je contacte Burger'S au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -23903,6 +25636,13 @@
           <t>Bonjour,
 Je contacte Bohēbon au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -23995,6 +25735,13 @@
           <t>Bonjour,
 Je contacte Pokawa au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -24087,6 +25834,13 @@
           <t>Bonjour,
 Je contacte Konapoke au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -24179,6 +25933,13 @@
           <t>Bonjour,
 Je contacte Poke &amp; Moi au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -24271,6 +26032,13 @@
           <t>Bonjour,
 Je contacte PizzaCosy au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -24363,6 +26131,13 @@
           <t>Bonjour,
 Je contacte Pizza Time au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -24455,6 +26230,13 @@
           <t>Bonjour,
 Je contacte La Boîte à Pizza au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -24547,6 +26329,13 @@
           <t>Bonjour,
 Je contacte Maison Bécam au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -24639,6 +26428,13 @@
           <t>Bonjour,
 Je contacte La Panetière au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -24731,6 +26527,13 @@
           <t>Bonjour,
 Je contacte Augustin au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -24823,6 +26626,13 @@
           <t>Bonjour,
 Je contacte Club Café au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -24915,6 +26725,13 @@
           <t>Bonjour,
 Je contacte ETIENNE Coffee &amp; Shop au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -25007,6 +26824,13 @@
           <t>Bonjour,
 Je contacte Beer's Corner au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -25099,6 +26923,13 @@
           <t>Bonjour,
 Je contacte Assiette au Bœuf au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -25191,6 +27022,13 @@
           <t>Bonjour,
 Je contacte Mister Garden au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -25283,6 +27121,13 @@
           <t>Bonjour,
 Je contacte Enjoy Tacos au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -25375,6 +27220,13 @@
           <t>Bonjour,
 Je contacte Tacos Avenue au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -25467,6 +27319,13 @@
           <t>Bonjour,
 Je contacte Terranimo au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -25559,6 +27418,13 @@
           <t>Bonjour,
 Je contacte La Croquetterie au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -25651,6 +27517,13 @@
           <t>Bonjour,
 Je contacte Le Cercle de la Vap au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -25743,6 +27616,13 @@
           <t>Bonjour,
 Je contacte Clopinette au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -25835,6 +27715,13 @@
           <t>Bonjour,
 Je contacte Naturalia au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -25927,6 +27814,13 @@
           <t>Bonjour,
 Je contacte So.bio au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -26019,6 +27913,13 @@
           <t>Bonjour,
 Je contacte Les Comptoirs de la Bio au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -26111,6 +28012,13 @@
           <t>Bonjour,
 Je contacte Le Comptoir de Mathilde au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -26203,6 +28111,13 @@
           <t>Bonjour,
 Je contacte Grain de Malice au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -26295,6 +28210,13 @@
           <t>Bonjour,
 Je contacte Pause Café au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -26387,6 +28309,13 @@
           <t>Bonjour,
 Je contacte Cash and Repair au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -26479,6 +28408,13 @@
           <t>Bonjour,
 Je contacte Akses au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -26571,6 +28507,13 @@
           <t>Bonjour,
 Je contacte Pixou Phone Emergency au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -26663,6 +28606,13 @@
           <t>Bonjour,
 Je contacte Phone Cash au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -26755,6 +28705,13 @@
           <t>Bonjour,
 Je contacte Save au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -26847,6 +28804,13 @@
           <t>Bonjour,
 Je contacte Lissac au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -26939,6 +28903,13 @@
           <t>Bonjour,
 Je contacte Yes Eye au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -27031,6 +29002,13 @@
           <t>Bonjour,
 Je contacte Intérieurs Privés au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -27123,6 +29101,13 @@
           <t>Bonjour,
 Je contacte Heytens au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -27215,6 +29200,13 @@
           <t>Bonjour,
 Je contacte MiLOME au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -27307,6 +29299,13 @@
           <t>Bonjour,
 Je contacte Quadro au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -27399,6 +29398,13 @@
           <t>Bonjour,
 Je contacte La Grande Récré au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -27491,6 +29497,13 @@
           <t>Bonjour,
 Je contacte Comtesse du Barry au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -27583,6 +29596,13 @@
           <t>Bonjour,
 Je contacte Temporis au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -27675,6 +29695,13 @@
           <t>Bonjour,
 Je contacte Shiva au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -27767,6 +29794,13 @@
           <t>Bonjour,
 Je contacte Petits-fils au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -27859,6 +29893,13 @@
           <t>Bonjour,
 Je contacte Kangourou Kids au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -27951,6 +29992,13 @@
           <t>Bonjour,
 Je contacte Les Déménageurs Bretons au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -28043,6 +30091,13 @@
           <t>Bonjour,
 Je contacte L'Orange Bleue au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -28135,6 +30190,13 @@
           <t>Bonjour,
 Je contacte Guy Hoquet l'Immobilier au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -28227,6 +30289,13 @@
           <t>Bonjour,
 Je contacte ERA Immobilier au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -28319,6 +30388,13 @@
           <t>Bonjour,
 Je contacte Arthurimmo.com au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -28411,6 +30487,13 @@
           <t>Bonjour,
 Je contacte Senior Compagnie au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -28503,6 +30586,13 @@
           <t>Bonjour,
 Je contacte Adhap Services au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -28595,6 +30685,13 @@
           <t>Bonjour,
 Je contacte Speedy au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -28687,6 +30784,13 @@
           <t>Bonjour,
 Je contacte Rent A Car au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -28779,6 +30883,13 @@
           <t>Bonjour,
 Je contacte Eléphant Bleu au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -28871,6 +30982,13 @@
           <t>Bonjour,
 Je contacte Ucar au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -28963,6 +31081,13 @@
           <t>Bonjour,
 Je contacte ADA au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -29055,6 +31180,13 @@
           <t>Bonjour,
 Je contacte Fix Auto France au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -29147,6 +31279,13 @@
           <t>Bonjour,
 Je contacte Stéphane Plaza Immobilier au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -29239,6 +31378,13 @@
           <t>Bonjour,
 Je contacte L'Adresse au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -29331,6 +31477,13 @@
           <t>Bonjour,
 Je contacte Apef au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -29423,6 +31576,13 @@
           <t>Bonjour,
 Je contacte Domidom au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -29515,6 +31675,13 @@
           <t>Bonjour,
 Je contacte Free Dom au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -29607,6 +31774,13 @@
           <t>Bonjour,
 Je contacte Age d'Or Services au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -29699,6 +31873,13 @@
           <t>Bonjour,
 Je contacte Babychou Services au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -29791,6 +31972,13 @@
           <t>Bonjour,
 Je contacte Family Sphere au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -29883,6 +32071,13 @@
           <t>Bonjour,
 Je contacte Les Menus Services au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -29975,6 +32170,13 @@
           <t>Bonjour,
 Je contacte Tchip Coiffure au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -30067,6 +32269,13 @@
           <t>Bonjour,
 Je contacte Saint Algue au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -30159,6 +32368,13 @@
           <t>Bonjour,
 Je contacte Jean Louis David au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -30251,6 +32467,13 @@
           <t>Bonjour,
 Je contacte Camille Albane au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -30343,6 +32566,13 @@
           <t>Bonjour,
 Je contacte Esthetic Center au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -30435,6 +32665,13 @@
           <t>Bonjour,
 Je contacte Keep Cool au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -30527,6 +32764,13 @@
           <t>Bonjour,
 Je contacte Episod au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -30619,6 +32863,13 @@
           <t>Bonjour,
 Je contacte Complétude au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -30711,6 +32962,13 @@
           <t>Bonjour,
 Je contacte Midas au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -30803,6 +33061,13 @@
           <t>Bonjour,
 Je contacte Point S au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -30895,6 +33160,13 @@
           <t>Bonjour,
 Je contacte Monsieur Store au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -30987,6 +33259,13 @@
           <t>Bonjour,
 Je contacte Tryba au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -31079,6 +33358,13 @@
           <t>Bonjour,
 Je contacte Wall Street English au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -31171,6 +33457,13 @@
           <t>Bonjour,
 Je contacte Coiff&amp;Co au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -31262,8 +33555,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Groupe Giboire. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -31353,8 +33653,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Groupe Carrère. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -31444,8 +33751,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Promomidi. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -31535,8 +33849,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter UTEI. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -31626,8 +33947,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Groupe Pichet. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -31717,8 +34045,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Nacarat. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -31808,8 +34143,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Lamotte. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -31899,8 +34241,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Nexity. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -31990,8 +34339,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Altarea Cogedim. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -32081,8 +34437,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Promologis. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -32172,8 +34535,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Constructa. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -32263,8 +34633,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Vinci Immobilier. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -32354,8 +34731,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter iad. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -32445,8 +34829,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter SAFTI. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -32536,8 +34927,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Capifrance. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -32627,8 +35025,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter BSK Immobilier. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -32718,8 +35123,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Propriétés Privées. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -32809,8 +35221,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Optimhome. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -32900,8 +35319,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Liberkeys. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -32991,8 +35417,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Hexaom (ex-Maisons France Confort). Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -33082,8 +35515,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Natilia. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -33173,8 +35613,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Les Jardins d'Arcadie. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -33264,8 +35711,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Ovelia. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -33355,8 +35809,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Domitys. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -33446,8 +35907,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Kley (The Boost Society). Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -33537,8 +36005,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Hife (The Boost Society). Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -33628,8 +36103,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Studélites. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -33719,8 +36201,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Twenty Campus. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -33810,8 +36299,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Colonies. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -33901,8 +36397,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter In'li. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -33992,8 +36495,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Homeloop. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -34083,8 +36593,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Atulam. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -34174,8 +36691,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Maugin. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -34265,8 +36789,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Fermetures Vitale. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -34356,8 +36887,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Ouvêo. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -34447,8 +36985,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Akena Vérandas. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -34538,8 +37083,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Vie &amp; Véranda. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -34629,8 +37181,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Vérandaline. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -34720,8 +37279,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Piscines Desjoyaux. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -34811,8 +37377,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Aboral Piscines. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -34902,8 +37475,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Léa Composites. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -34993,8 +37573,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Mondial Piscine. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -35084,8 +37671,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Nextpool. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -35175,8 +37769,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter BCI. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -35266,8 +37867,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Tschoeppé. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -35357,8 +37965,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Charuel. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -35448,8 +38063,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Cetal. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -35539,8 +38161,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Maine Clôtures. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -35630,8 +38259,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Clôture Fermetures Portail (CFP). Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -35721,8 +38357,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Closura. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -35812,8 +38455,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Baudet. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -35903,8 +38553,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Capremib. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -35994,8 +38651,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Kramer. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -36085,8 +38749,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Bonnin-Charbonneau. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -36176,8 +38847,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Solewa. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -36267,8 +38945,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Soleil du Sud. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -36358,8 +39043,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter France Solar. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -36449,8 +39141,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Denis Matériaux. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -36540,8 +39239,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Perin. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -36631,8 +39337,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Aditec. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -36722,8 +39435,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Voltaïca. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -36813,8 +39533,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Énergies de Loire. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -36904,8 +39631,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Terre et Lac. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -36995,8 +39729,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Airwell Industrie. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -37086,8 +39827,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Ateliers Halimi. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -37177,8 +39925,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Groupe Loubat. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -37268,8 +40023,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Soprofen. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -37359,8 +40121,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Aluroy. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -37450,8 +40219,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter France Fermetures. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -37541,8 +40317,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Deprat. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -37632,8 +40415,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Profalux. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -37723,8 +40513,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Néova (groupe Néoform). Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -37814,8 +40611,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Groupe Fournier Habitat. Nos équipes réalisent des vidéos motion design pour les entreprises du bâtiment et de l'énergie : présentation de gamme, vidéo de salon, recrutement, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont deux vidéos réalisées pour un acteur des menuiseries et du vitrage : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous envoyer une proposition de script gratuite.
+Vidéo de présentation à partir de 390 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -37905,8 +40709,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Pack'R. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -37996,8 +40807,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Van Den Casteele. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -38087,8 +40905,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Barriquand Technologies Thermiques. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -38178,8 +41003,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Meca-Inox. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -38269,8 +41101,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Coraxes. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -38360,8 +41199,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter FMV Defrance. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -38451,8 +41297,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Polieco France. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -38542,8 +41395,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter CJ Plast. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -38633,8 +41493,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Chrystal Plastic. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -38724,8 +41591,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Hebeco Plastic. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -38815,8 +41689,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Plast3C. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -38906,8 +41787,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter DATK. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -38997,8 +41885,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Team Plastique. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -39088,8 +41983,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Stiplastics. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -39179,8 +42081,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter FMA Concept. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -39270,8 +42179,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Mecam 44. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -39361,8 +42277,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Polymécanic. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -39452,8 +42375,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter H2 Mécanique. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -39543,8 +42473,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Geslin SAS. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -39634,8 +42571,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Technature. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -39725,8 +42669,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Bretim. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -39816,8 +42767,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Bretinov. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -39907,8 +42865,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Groupe Quéguiner. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -39998,8 +42963,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Rossi Aero. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -40089,8 +43061,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Niryo. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -40180,8 +43159,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Shark Robotics. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -40271,8 +43257,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter EMSFactory. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -40362,8 +43355,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Nor-Feed. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -40453,8 +43453,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Billard Engrenages. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -40544,8 +43551,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter ECP. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -40635,8 +43649,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Airborne. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -40726,8 +43747,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Aluminor. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -40817,8 +43845,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Ardamez. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -40908,8 +43943,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Art et Floritude. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -40999,8 +44041,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Collinet. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -41090,8 +44139,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Fermob. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -41181,8 +44237,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Hotelys. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -41272,8 +44335,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Malvaux Interior. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -41363,8 +44433,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Meubles Célio. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -41454,8 +44531,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Resistub Productions. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -41545,8 +44629,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Thiriez Literie. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -41636,8 +44727,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Tissages Denantes. Nos équipes réalisent des vidéos motion design pour l'industrie : vidéo de stand pour les salons, présentation produit, export en plus de 25 langues, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
+Vidéo de présentation à partir de 390 € HT, chaque langue supplémentaire 90 € HT. Seriez vous disponible pour en parler ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -41727,6 +44825,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Bull. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -41818,6 +44923,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Banque Populaire Bourgogne Franche-Comté. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -41909,6 +45021,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Forvis Mazars (Grand Ouest). Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -42000,6 +45119,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter In Extenso. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -42091,6 +45217,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter E.Leclerc. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -42182,6 +45315,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Apave. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -42273,6 +45413,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Astek. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -42364,6 +45511,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Scalian. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -42455,6 +45609,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Daher. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -42546,6 +45707,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Wavestone. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -42637,6 +45805,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter EDF (Auvergne-Rhône-Alpes). Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -42728,6 +45903,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Safran (site de Rennes-La Janais / Fougères). Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -42819,6 +46001,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter OpenClassrooms. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -42910,6 +46099,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Studi. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -43001,6 +46197,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter IFOCOP. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -43092,6 +46295,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter CESI. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -43183,6 +46393,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter EPITECH. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -43274,6 +46491,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter IPSA. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -43365,6 +46589,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter EFAP. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -43456,6 +46687,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter ISEG. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -43547,6 +46785,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter ESSCA. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -43638,6 +46883,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter KEDGE Business School. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -43729,6 +46981,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter NEOMA Business School. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -43820,6 +47079,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Gobelins Paris. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -43911,6 +47177,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Wild Code School. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -44002,6 +47275,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter O'clock. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -44093,6 +47373,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Groupe IGS. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -44184,6 +47471,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter IPSSI. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -44275,6 +47569,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter ISCOD. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -44366,6 +47667,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter ESTIAM. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -44457,6 +47765,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter EDHEC Business School. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -44548,6 +47863,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Compagnons du Devoir. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -44639,8 +47961,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Sandaya. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -44730,8 +48059,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Huttopia. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -44821,8 +48157,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Capfun. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -44912,8 +48255,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Yelloh! Village. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -45003,8 +48353,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Belambra Clubs. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -45094,8 +48451,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Siblu. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -45185,8 +48549,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Les Castels. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -45276,8 +48647,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Tohapi. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -45367,8 +48745,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Vulcania. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -45458,8 +48843,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Le PAL. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -45549,8 +48941,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter OKKO Hotels. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -45640,8 +49039,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Big Mamma Group. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -45731,8 +49137,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Groupe Bertrand. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -45822,8 +49235,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Office de Tourisme du Lac d'Annecy. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -45913,8 +49333,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Vivalto Santé. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -46004,8 +49431,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Almaviva Santé. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -46095,8 +49529,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Point Vision. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -46186,8 +49627,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Colisée. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -46277,8 +49725,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Groupe Vidi. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -46368,8 +49823,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Cerballiance. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -46459,8 +49921,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Mutuelle de Poitiers Assurances. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -46550,8 +50019,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Dentego. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -46641,8 +50117,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Dentylis. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -46732,8 +50215,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Mutuelle Ociane Matmut. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -46823,8 +50313,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Hôpital privé Ambroise Paré – Hartmann. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -46914,8 +50411,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter RX France. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -47005,8 +50509,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Viparis. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -47096,8 +50607,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Festival des Vieilles Charrues. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -47187,8 +50705,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Hellfest. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -47278,8 +50803,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Les Eurockéennes de Belfort. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -47369,8 +50901,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Garorock. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -47460,8 +50999,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Stade Toulousain. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -47551,8 +51097,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter LOU Rugby. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -47642,8 +51195,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Racing Club de Lens. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -47733,8 +51293,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Montpellier Handball. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -47824,8 +51391,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Paris Basketball. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -47915,8 +51489,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter La Seine Musicale. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -48006,8 +51587,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Réalités. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -48097,8 +51685,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Gambetta. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -48188,8 +51783,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Edouard Denis. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -48279,8 +51881,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Angelotti. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -48370,8 +51979,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Ogic. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -48461,8 +52077,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Efficity. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -48552,8 +52175,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Les Senioriales. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -48643,8 +52273,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Pichet. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -48734,8 +52371,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Marignan. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -48821,8 +52465,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Enedis. Nos équipes réalisent des vidéos motion design pour les entreprises : marque employeur, recrutement, présentation de produits et vidéos de stand pour les salons, livrées en 7 jours, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo réalisée pour un acteur du bâtiment : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
+Vidéo de présentation à partir de 390 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -48908,8 +52559,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Bouygues. Nos équipes réalisent des vidéos motion design pour les entreprises : marque employeur, recrutement, présentation de produits et vidéos de stand pour les salons, livrées en 7 jours, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo réalisée pour un acteur du bâtiment : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
+Vidéo de présentation à partir de 390 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -48995,8 +52653,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Thales. Nos équipes réalisent des vidéos motion design pour les entreprises : marque employeur, recrutement, présentation de produits et vidéos de stand pour les salons, livrées en 7 jours, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo réalisée pour un acteur du bâtiment : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
+Vidéo de présentation à partir de 390 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -49082,8 +52747,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Saint-Gobain Glass. Nos équipes réalisent des vidéos motion design pour les entreprises : marque employeur, recrutement, présentation de produits et vidéos de stand pour les salons, livrées en 7 jours, dans plus de 25 langues.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo réalisée pour un acteur du bâtiment : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
+Vidéo de présentation à partir de 390 € HT. Je peux vous adresser une proposition adaptée à vos besoins actuels.
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -49174,6 +52846,13 @@
           <t>Bonjour,
 Je contacte Laforêt au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -49266,6 +52945,13 @@
           <t>Bonjour,
 Je contacte Century 21 France au sujet de la vidéo. Un réseau qui grandit a besoin de contenus en continu : recrutement de franchisés, ouvertures, promotions locales pour les réseaux sociaux de chaque point de vente.
 Nos équipes réalisent des vidéos motion design livrées en 7 jours, déclinables par ville ou par agence, dans tous les formats (LinkedIn, Instagram, TikTok).
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Nous proposons un abonnement à 890 € HT par mois pour 4 vidéos courtes. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
@@ -49357,6 +53043,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Groupe RATP. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -49448,6 +53141,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Groupe BPCE. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -49539,6 +53239,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Caisse d'Épargne CEPAC. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -49630,6 +53337,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Caisse d'Épargne Côte d'Azur. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -49721,6 +53435,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Macif. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -49812,6 +53533,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter SNCF. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -49903,6 +53631,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Transdev. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -49994,6 +53729,13 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Afpa. Nos équipes réalisent des vidéos motion design de recrutement et de présentation : métiers, valeurs, parcours, avec voix off et musique, pour LinkedIn, Instagram et TikTok, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations, dont une vidéo de recrutement : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
 Vidéo de recrutement à partir de 690 € HT. Je peux vous envoyer une proposition de script gratuite.
 Bien cordialement,
@@ -50085,8 +53827,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Elsan. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -50176,8 +53925,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter GL events. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -50267,8 +54023,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Comexposium. Nos équipes réalisent des vidéos motion design de présentation, de promotion et de recrutement, avec voix off et musique, dans plus de 25 langues pour une clientèle internationale, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 990 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo courte à partir de 390 € HT, vidéo de présentation à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -50358,8 +54121,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter Kaufman &amp; Broad. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo
@@ -50449,8 +54219,15 @@
         <is>
           <t>Bonjour,
 Je me permets de contacter IAD France. Nos équipes réalisent des vidéos motion design pour l'immobilier : lancement de programme, présentation de biens, recrutement d'agents, avec voix off et musique, livrées en 7 jours.
+Nos tarifs, tout compris (script, voix off, musique, animation, 2 séries de retouches, livraison en 7 jours) :
+Vidéo courte, 15 à 20 secondes : 390 € HT
+Vidéo promo, 30 à 45 secondes : 690 € HT
+Vidéo de présentation, 45 à 60 secondes : 990 € HT
+Abonnement, 4 vidéos courtes par mois : 890 € HT par mois
+Format vertical ou langue supplémentaire : 90 € HT
+Je peux aussi vous envoyer des exemples de vidéos adaptés à votre secteur.
 Nos réalisations : https://dgjmfrbv4k-lab.github.io/NOXEM-GROUP/piwa/?v=2#nointro
-Vidéo de présentation à partir de 990 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
+Vidéo de présentation à partir de 390 € HT, vidéo courte réseaux sociaux à partir de 390 € HT. Seriez vous disponible pour un échange de 10 minutes ?
 Bien cordialement,
 Kevin
 PIWA, studio vidéo

--- a/prospection/prospects-PIWA-500.xlsx
+++ b/prospection/prospects-PIWA-500.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1850,6 +1850,853 @@
         </is>
       </c>
       <c r="G38" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>(33 sociétés déjà contactées)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>réponse dans chaque conversation</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Complément : tous les tarifs dès 390 € HT + exemples sur demande</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Envoyé</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Laforêt</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>contact-laforet@laforet.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Des vidéos pour tout le réseau Laforêt, dès 390 € HT</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Keep Cool</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>contact@keepcool.fr</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Des vidéos pour tout le réseau Keep Cool, dès 390 € HT</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>presse@ada.fr</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Des vidéos pour tout le réseau ADA, dès 390 € HT</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Elsan</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>news@elsan.care</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Une vidéo pour Elsan, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Groupe BPCE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>presse@bpce.fr</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Une vidéo pour le Groupe BPCE, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Groupe RATP</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>servicedepresse@ratp.fr</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Une vidéo pour le Groupe RATP, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Bouygues</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>presse@bouygues.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Une vidéo pour Bouygues, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pichet</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>contact@pichet.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Une vidéo pour Pichet, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Niryo</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>contact@niryo.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Une vidéo pour Niryo, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Technature</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>info@tech-nature.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Une vidéo pour Technature, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Enedis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>service-presse@enedis.fr</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Une vidéo pour Enedis, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mutuelle de Poitiers Assurances</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>accueil@mutuelledepoitiers.fr</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Une vidéo pour Mutuelle de Poitiers Assurances, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Seb</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>presse@groupeseb.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Une vidéo pour le Groupe SEB, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>DomusVi</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>press@domusvi.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Une vidéo pour DomusVi, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>OVHcloud</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>media@ovhcloud.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Une vidéo pour OVHcloud, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Teleperformance</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>tppublicaffairs@teleperformance.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Une vidéo pour Teleperformance, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Getlink</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>press@getlinkgroup.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Une vidéo pour Getlink, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>bioMérieux</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>media@biomerieux.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Une vidéo pour bioMérieux, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Servier</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>presse@servier.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Une vidéo pour Servier, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Air Liquide</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>media@airliquide.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Une vidéo pour Air Liquide, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Alstom</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>mediarelations@alstomgroup.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Une vidéo pour Alstom, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Groupe Beneteau</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>presse@beneteau-group.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Une vidéo pour le Groupe Beneteau, dès 390 € HT, livrée en 7 jours</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
         <is>
           <t>12/10/2026</t>
         </is>

--- a/prospection/prospects-PIWA-500.xlsx
+++ b/prospection/prospects-PIWA-500.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1886,7 +1886,6 @@
           <t>Envoyé</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2699,6 +2698,5626 @@
       <c r="G61" t="inlineStr">
         <is>
           <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Bretagne Côte de Granit Rose</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>contact@bretagne-cotedegranitrose.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Guingamp - Baie de Paimpol</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>tourisme@guingamp-paimpol.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Office de Tourisme du Pays des Abers</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>office@abers-tourisme.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Office de Tourisme de Fougères</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>tourisme@ot-fougeres.fr</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Office de Tourisme de Carnac</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>accueiltourisme@ot-carnac.fr</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Office de Tourisme du Pays d'Aubagne et de l'Etoile</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>accueil@tourisme-paysdaubagne.fr</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Office de Tourisme des Alpes du Léman</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>info@alpesduleman.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Office de Tourisme d'Oz-en-Oisans</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>info@oz-en-oisans.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Grenoble Alpes</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>info@grenoble-tourisme.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Office de Tourisme de Serre Chevalier Vallée Briançon</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>contact@serrechevalier.fr</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Office de Tourisme des Deux Alpes</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>info@les2alpes.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Castelnaudary Lauragais Audois</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>accueil@castelnaudary-tourisme.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Office de Tourisme et des Congrès Montpellier Méditerranée Métropole</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>contact@ot-montpellier.fr</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Office Municipal de Tourisme de Carcassonne</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>accueil@carcassonne-tourisme.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Office de Tourisme de Mauguio Carnon</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>officedetourisme@mauguio-carnon.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Office de Tourisme de Rodez Agglomération</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>infos@tourisme.myrodez.fr</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Grand Narbonne Tourisme</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>info@grandnarbonnetourisme.fr</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Office de Tourisme du Grand Montauban</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>info@montauban-tourisme.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Grand Orb</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>contact@tourisme-grandorb.fr</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>OTI Pyrénées Méditerranée</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>contact@pymed.fr</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Office de Tourisme et des Congrès de Caen la Mer</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>info@caenlamer-tourisme.fr</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Drôme Attractivité</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>info@drome-attractivite.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Destination Royan Atlantique</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>contact@royanatlantique.fr</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Office de Tourisme de Strasbourg et sa Région</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>info@visitstrasbourg.fr</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Office de Tourisme d'Obernai</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>info@tourisme-obernai.fr</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Pays de Langres</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>info@tourisme-langres.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Contrexéville Tourisme</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>info@contrextourisme.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Office de Tourisme de la Région de Molsheim-Mutzig</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>infos@ot-molsheim-mutzig.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Office de Tourisme du Grand Verdun</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>contact@tourisme-verdun.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Métropolitain Nice Côte d'Azur</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>info@nicecotedazurtourisme.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Office de Tourisme de Dijon Métropole</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>info@otdijon.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Sud Vendée Littoral Tourisme</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>info@sudvendeelittoral.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Vendée Grand Sud</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>tourisme@vendeegrandsud.fr</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Intercommunal de Pornic</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>info@pornic.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Office de Tourisme du Pays d'Ajaccio</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>info@ajaccio-tourisme.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Intercommunal Calvi Balagne</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>tourisme@balagne-corsica.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Intercommunal Ouest Corsica (Cargèse)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>cargese@ouestcorsica.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Pays Basque (Saint-Jean-de-Luz)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>saintjeandeluz@otpaysbasque.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Office de Tourisme du Bazadais (Sud Gironde)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>bazas@tourisme-sud-gironde.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Bourg Cubzaguais</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>tourismebourg@grand-cubzaguais.fr</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Office de Tourisme du Grand Dax</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>info@dax-tourisme.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Office de Tourisme de Seignosse</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>contact@seignosse-tourisme.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Royat-Chamalières</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>info@ot-royat.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Office de Tourisme des Combrailles</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>contact@tourisme-combrailles.fr</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Mond'Arverne</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>info@mondarverne.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Office de Tourisme du Carladès</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>tourisme@carlades.fr</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Vallée de Chamonix-Mont-Blanc</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>info@chamonix.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Office de Tourisme de Manigod</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>info@manigod.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Office de Tourisme de Châtel</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>touristoffice@chatel.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Sallanches Tourisme</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>tourisme@sallanches.com</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Méribel Tourisme</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>info@meribel.net</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Saint-Jean-d'Arves - Les Sybelles</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>info@sja73.com</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Office de Tourisme de La Toussuire</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>info@la-toussuire.com</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Office de Tourisme Intercommunal Pays d'Apt Luberon</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>oti@paysapt-luberon.fr</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Camping La Rouveyrolle</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>info@campingrouveyrolle.fr</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Domaine Arleblanc Camping</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>info@arleblanc.com</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Camping de la Plage (Neyrac-les-Bains)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>contact@lecampingdelaplage.com</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Camping Nature Parc l'Ardéchois</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>info@ardechois-camping.com</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Camping de la Baie</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>contact@campingdelabaie.com</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Camping de la Plage</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>contact@camping-plage.com</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Camping Lou Castel</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>contact@loucastel.com</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Hôtel La Croix de Savoie &amp; Spa</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>info@lacroixdesavoie.fr</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Yelloh! Village Au Lac de Biscarrosse</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>contact@aulacdebiscarrosse.com</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Camping Bonporteau</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>contact@bonporteau.fr</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Camping Domaine de la Cigalière</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>contact@domaine-lacigaliere.com</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Hôtel Windsor Biarritz</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>contact@hotelwindsorbiarritz.com</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Airotel Camping La Côte d'Argent</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>info@camping-cote-dargent.com</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Camping Airotel L'Océan</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>contact@airotel-ocean.com</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Yelloh! Village Le Sérignan Plage</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>info@yellohvillage-serignan-plage.com</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Camping Hélios</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>contact@camping-helios.com</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Waga Energy</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>media@waga-energy.com</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Lumibird</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>info@lumibird.com</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Alvea Formation (IFAC) - site Nantes</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>contact@alveaformation-ifac.com</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Emergitude - site Nantes</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>contact@emergitude.fr</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ARTEK Formations</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>contact@artek-formations.fr</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Digital School of Paris</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>contact@digitalschool.paris</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Collège privé La Boétie (École La Boétie)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>contact@ecolelaboetie.com</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>AREFOR</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>accueil@arefor.fr</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>ADEF</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>accueil@adef-asso.com</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>BIRD Formation</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>contact@birdformation.com</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>IAE Lille University School of Management</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>contact@iaelille.fr</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>IFRIA Pays de la Loire (CFA des industries alimentaires)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>contact@ifria-ouest.fr</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>École des Établières (antenne La Roche-sur-Yon)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>infos@etablieres.fr</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>BTP CFA Maine-et-Loire</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>contact-49@btpcfa-pdl.com</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Propuls' - site Angers</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>dossiers@propuls.fr</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Orient'Action - Novaxis, site du Mans</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>info@orientaction.com</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>MSR Métallerie</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>contact@msr-metallerie.fr</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Technifil</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>contact@technifil01.fr</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>NUMER'US</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>accueil@numerus.fr</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Énergies Vertes Occitanie</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>contact@solaireoccitanie.fr</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>OcciSun</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>contact@occisun.fr</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>FCS</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>contact@fcs78.fr</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1001 Soleils</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>contact@soleils.biz</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Enerconfort</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>contact@enerconfort.com</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PVSO</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>contact@pvso.fr</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Coegy</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>contact@coegy.fr</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Iso-Solaire</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>contact@iso-solaire.fr</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>EGCF</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>contact@egcf.fr</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Photovolt</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>contact@photovolt.fr</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Electric Connexion</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>contact@electric-connexion.com</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>EUNF</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>contact@eunf.fr</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Monabee</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>com@monabee.fr</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>ÉCHEC : bloqué par le serveur du destinataire</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>BGELEC</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>contact@b-gelec.fr</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ABplus Solaire</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>contact@abplus-solaire.fr</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>BATI-ECO 13</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>contact@bati-eco13.com</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Autan Solaire</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>contact@autansolaire.fr</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>C2EF</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>contact@c2ef.fr</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Ceneo énergie</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>contact@ceneo.fr</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Solaire Declic</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>contact@solairedeclic.fr</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Captain Solar</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>contact@captainsolar.fr</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Optimwatt</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>contact@optimwatt.fr</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Libow</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>contact@libow.fr</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>TAMSOL</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>contact@tamsol.fr</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Qualis Energies</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>contact@qualis-energies.fr</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>RDG Energy</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>contact@rdg-energy-solaire.fr</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>INNOVASUN</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>contact@innovasun.fr</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Circuit Court Énergie</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>contact@circuitcourt-energie.com</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Bretagne Antennes</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>bonjour@bretagne-antennes.bzh</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Golfe Eco Energie</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>contact@gee.bzh</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Lantrain Électricité</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>contact@lantrain-electricite.fr</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Breizh Domotic</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>contact@breizhdomotic.fr</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Triballier Lamanda</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>contact@ets-triballier.com</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Quénéa Énergies Renouvelables</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>commercial@quenea.com</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>C.E.R.I.S.E.S.</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>contact@cerises-solaire.fr</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Yaco Solaire</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>contact@yaco-solaire.com</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Logyk Energie</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>contact@logyk.fr</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Solely</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>contact@solely.fr</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>MD Energie 74</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>contact@md-energie.fr</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Cevoha</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>contact@cevoha.fr</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ERM Energies</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>contact@erm-energies.com</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Sud Concept</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>info@sud-concept.com</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Boulze</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>contact@boulze.fr</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>K-Helios</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>contact@k-helios.fr</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Aguisol Photovoltaïque</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>contact@aguisol-photovoltaique.com</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>HydroAlsace</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>contact@hydroalsace.com</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Klein Patrick Électricité</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>info@electricite-klein.com</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>My Electricity</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>hello@myelectricity.fr</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Calisun</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>gestion@calisun.fr</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>WALLIX</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>info@wallix.com</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Nabla</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>contact@nabla.com</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Sunology</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>contact@sunology.eu</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>ASM Clermont Auvergne</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>partenariat@asm-rugby.com</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Vivalto Santé</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>contactpresse@vivalto-sante.com</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Hellfest Productions</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>info@hellfest.fr</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>LOSC Lille</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>contact@losc.fr</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Groupe Bertrand - Carré des Invalides</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>carre-des-invalides@groupe-bertrand.com</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Les Eurockéennes de Belfort</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>festival@eurockeennes.fr</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>We Love Green</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>contact@welovegreen.fr</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>RC Toulon</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>contact@rctoulon.com</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Comexposium - Salon National de l'Immobilier</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>salonimmobilier@comexposium.com</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>GL events - Hyvolution</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>hyvolution@gl-events.com</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Olympique de Marseille</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>digital@om.net</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Une vidéo pour …, dès 390 € HT (personnalisé)</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>piwastudiopiwastudio@gmail.com</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Envoyé, pas de retour en erreur</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
         </is>
       </c>
     </row>
